--- a/data/Mappings/mapping_tailing.xlsx
+++ b/data/Mappings/mapping_tailing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/data/Mappings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7A5274D-7810-46C8-B4CE-94FE6858DBFA}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1193B88A-7CFB-4AB9-AFF7-900DABFD721F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LT" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LT!$A$1:$G$599</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mapping!$A$1:$B$91</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="641">
   <si>
     <t>main_id</t>
   </si>
@@ -1993,10 +1994,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2012,6 +2012,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2277,19 +2281,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G599"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2312,7 +2317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2335,7 +2340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -2358,7 +2363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -2381,7 +2386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2404,7 +2409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2427,7 +2432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2450,7 +2455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2473,7 +2478,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2496,7 +2501,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2519,7 +2524,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2542,7 +2547,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -2565,7 +2570,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -2588,7 +2593,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -2611,7 +2616,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -2634,7 +2639,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -2657,7 +2662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -2680,7 +2685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2703,7 +2708,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,7 +2731,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2749,7 +2754,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -2772,7 +2777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -2795,7 +2800,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -2818,7 +2823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -2841,7 +2846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
@@ -2864,7 +2869,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,7 +2892,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -2910,7 +2915,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -2933,7 +2938,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -2956,7 +2961,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -2979,7 +2984,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -3002,7 +3007,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -3025,7 +3030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -3048,7 +3053,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
@@ -3071,7 +3076,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -3094,7 +3099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -3117,7 +3122,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
@@ -3140,7 +3145,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,7 +3168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
@@ -3186,7 +3191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
@@ -3209,7 +3214,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>51</v>
       </c>
@@ -3232,7 +3237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>51</v>
       </c>
@@ -3255,7 +3260,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -3278,7 +3283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
@@ -3301,7 +3306,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -3324,7 +3329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3347,7 +3352,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -3370,7 +3375,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -3393,7 +3398,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
@@ -3416,7 +3421,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -3439,7 +3444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -3462,7 +3467,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -3485,7 +3490,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -3508,7 +3513,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -3531,7 +3536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -3554,7 +3559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -3577,7 +3582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>59</v>
       </c>
@@ -3600,7 +3605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -3623,7 +3628,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -3646,7 +3651,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -3669,7 +3674,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>63</v>
       </c>
@@ -3692,7 +3697,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>66</v>
       </c>
@@ -3715,7 +3720,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -3738,7 +3743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>66</v>
       </c>
@@ -3761,7 +3766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -3784,7 +3789,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -3807,7 +3812,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>69</v>
       </c>
@@ -3830,7 +3835,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -3853,7 +3858,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
@@ -3876,7 +3881,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>72</v>
       </c>
@@ -3899,15 +3904,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>554</v>
       </c>
       <c r="B71" s="1">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C71" s="1">
-        <v>6050.17</v>
+        <v>841.15</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>73</v>
@@ -3922,81 +3927,81 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72" s="1">
-        <v>1124</v>
-      </c>
-      <c r="C72" s="1">
-        <v>6050.17</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E72" s="1" t="s">
+    <row r="72" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>555</v>
+      </c>
+      <c r="B72">
+        <v>1122</v>
+      </c>
+      <c r="C72">
+        <v>10587.23</v>
+      </c>
+      <c r="D72" t="s">
+        <v>556</v>
+      </c>
+      <c r="E72" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="1">
-        <v>100</v>
-      </c>
-      <c r="G72" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="1">
-        <v>1125</v>
-      </c>
-      <c r="C73" s="1">
-        <v>6050.17</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="F72">
+        <v>36.363636363636303</v>
+      </c>
+      <c r="G72">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>550</v>
+      </c>
+      <c r="B73">
+        <v>1122</v>
+      </c>
+      <c r="C73">
+        <v>1164.32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>551</v>
+      </c>
+      <c r="E73" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="1">
-        <v>100</v>
-      </c>
-      <c r="G73" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1126</v>
-      </c>
-      <c r="C74" s="1">
-        <v>6050.17</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="F73">
+        <v>31.578947368421002</v>
+      </c>
+      <c r="G73">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>557</v>
+      </c>
+      <c r="B74">
+        <v>1122</v>
+      </c>
+      <c r="C74">
+        <v>17605.02</v>
+      </c>
+      <c r="D74" t="s">
+        <v>558</v>
+      </c>
+      <c r="E74" t="s">
         <v>74</v>
       </c>
-      <c r="F74" s="1">
-        <v>100</v>
-      </c>
-      <c r="G74" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F74">
+        <v>25</v>
+      </c>
+      <c r="G74">
+        <v>11.1111111111111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B75" s="1">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="C75" s="1">
         <v>6050.17</v>
@@ -4014,15 +4019,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>72</v>
+        <v>554</v>
       </c>
       <c r="B76" s="1">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="C76" s="1">
-        <v>6050.17</v>
+        <v>6567.22</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>73</v>
@@ -4037,107 +4042,107 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="77" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77">
+        <v>1123</v>
+      </c>
+      <c r="C77">
+        <v>19830.419999999998</v>
+      </c>
+      <c r="D77" t="s">
+        <v>345</v>
+      </c>
+      <c r="E77" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77">
+        <v>28.571428571428498</v>
+      </c>
+      <c r="G77">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>555</v>
+      </c>
+      <c r="B78">
+        <v>1123</v>
+      </c>
+      <c r="C78">
+        <v>3544.58</v>
+      </c>
+      <c r="D78" t="s">
+        <v>556</v>
+      </c>
+      <c r="E78" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78">
+        <v>36.363636363636303</v>
+      </c>
+      <c r="G78">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>550</v>
+      </c>
+      <c r="B79">
+        <v>1123</v>
+      </c>
+      <c r="C79">
+        <v>7056.65</v>
+      </c>
+      <c r="D79" t="s">
+        <v>551</v>
+      </c>
+      <c r="E79" t="s">
+        <v>74</v>
+      </c>
+      <c r="F79">
+        <v>31.578947368421002</v>
+      </c>
+      <c r="G79">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>362</v>
+      </c>
+      <c r="B80">
+        <v>1123</v>
+      </c>
+      <c r="C80">
+        <v>17952.34</v>
+      </c>
+      <c r="D80" t="s">
+        <v>363</v>
+      </c>
+      <c r="E80" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80">
+        <v>42.105263157894697</v>
+      </c>
+      <c r="G80">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="1">
-        <v>1129</v>
-      </c>
-      <c r="C77" s="1">
+      <c r="B81" s="1">
+        <v>1124</v>
+      </c>
+      <c r="C81" s="1">
         <v>6050.17</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F77" s="1">
-        <v>100</v>
-      </c>
-      <c r="G77" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B78" s="1">
-        <v>1122</v>
-      </c>
-      <c r="C78" s="1">
-        <v>841.15</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F78" s="1">
-        <v>100</v>
-      </c>
-      <c r="G78" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1123</v>
-      </c>
-      <c r="C79" s="1">
-        <v>6567.22</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F79" s="1">
-        <v>100</v>
-      </c>
-      <c r="G79" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B80" s="1">
-        <v>1124</v>
-      </c>
-      <c r="C80" s="1">
-        <v>6567.22</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F80" s="1">
-        <v>100</v>
-      </c>
-      <c r="G80" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B81" s="1">
-        <v>1125</v>
-      </c>
-      <c r="C81" s="1">
-        <v>6567.22</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>73</v>
@@ -4152,12 +4157,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>554</v>
       </c>
       <c r="B82" s="1">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C82" s="1">
         <v>6567.22</v>
@@ -4175,76 +4180,76 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B83" s="1">
-        <v>1127</v>
-      </c>
-      <c r="C83" s="1">
-        <v>6567.22</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E83" s="1" t="s">
+    <row r="83" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>344</v>
+      </c>
+      <c r="B83">
+        <v>1124</v>
+      </c>
+      <c r="C83">
+        <v>19830.419999999998</v>
+      </c>
+      <c r="D83" t="s">
+        <v>345</v>
+      </c>
+      <c r="E83" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="1">
-        <v>100</v>
-      </c>
-      <c r="G83" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B84" s="1">
-        <v>1128</v>
-      </c>
-      <c r="C84" s="1">
-        <v>6567.22</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="F83">
+        <v>28.571428571428498</v>
+      </c>
+      <c r="G83">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>555</v>
+      </c>
+      <c r="B84">
+        <v>1124</v>
+      </c>
+      <c r="C84">
+        <v>3544.58</v>
+      </c>
+      <c r="D84" t="s">
+        <v>556</v>
+      </c>
+      <c r="E84" t="s">
         <v>74</v>
       </c>
-      <c r="F84" s="1">
-        <v>100</v>
-      </c>
-      <c r="G84" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B85" s="1">
-        <v>1129</v>
-      </c>
-      <c r="C85" s="1">
-        <v>6567.22</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="F84">
+        <v>36.363636363636303</v>
+      </c>
+      <c r="G84">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>550</v>
+      </c>
+      <c r="B85">
+        <v>1124</v>
+      </c>
+      <c r="C85">
+        <v>7056.65</v>
+      </c>
+      <c r="D85" t="s">
+        <v>551</v>
+      </c>
+      <c r="E85" t="s">
         <v>74</v>
       </c>
-      <c r="F85" s="1">
-        <v>100</v>
-      </c>
-      <c r="G85" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F85">
+        <v>31.578947368421002</v>
+      </c>
+      <c r="G85">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4267,7 +4272,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4290,7 +4295,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>78</v>
       </c>
@@ -4313,7 +4318,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>80</v>
       </c>
@@ -4336,7 +4341,7 @@
         <v>91.6666666666666</v>
       </c>
     </row>
-    <row r="90" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>83</v>
       </c>
@@ -4359,7 +4364,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>83</v>
       </c>
@@ -4382,7 +4387,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>86</v>
       </c>
@@ -4405,7 +4410,7 @@
         <v>85.714285714285694</v>
       </c>
     </row>
-    <row r="93" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>86</v>
       </c>
@@ -4428,7 +4433,7 @@
         <v>85.714285714285694</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>89</v>
       </c>
@@ -4451,7 +4456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>89</v>
       </c>
@@ -4474,7 +4479,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>92</v>
       </c>
@@ -4497,7 +4502,7 @@
         <v>76.923076923076906</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -4510,7 +4515,7 @@
       <c r="D97" t="s">
         <v>96</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" t="s">
         <v>97</v>
       </c>
       <c r="F97">
@@ -4520,7 +4525,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>95</v>
       </c>
@@ -4533,7 +4538,7 @@
       <c r="D98" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" t="s">
         <v>97</v>
       </c>
       <c r="F98">
@@ -4543,7 +4548,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>95</v>
       </c>
@@ -4556,7 +4561,7 @@
       <c r="D99" t="s">
         <v>96</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" t="s">
         <v>97</v>
       </c>
       <c r="F99">
@@ -4566,7 +4571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>319</v>
       </c>
@@ -4589,7 +4594,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>325</v>
       </c>
@@ -4612,7 +4617,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>98</v>
       </c>
@@ -4635,7 +4640,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -4658,7 +4663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -4681,7 +4686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>438</v>
       </c>
@@ -4704,7 +4709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -4727,7 +4732,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -4750,7 +4755,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -4773,7 +4778,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -4796,7 +4801,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -4819,7 +4824,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>107</v>
       </c>
@@ -4842,7 +4847,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>107</v>
       </c>
@@ -4865,7 +4870,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>107</v>
       </c>
@@ -4888,7 +4893,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>107</v>
       </c>
@@ -4911,7 +4916,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>411</v>
       </c>
@@ -4934,7 +4939,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>411</v>
       </c>
@@ -4957,7 +4962,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>411</v>
       </c>
@@ -4980,7 +4985,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>411</v>
       </c>
@@ -5003,7 +5008,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>411</v>
       </c>
@@ -5026,7 +5031,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>411</v>
       </c>
@@ -5049,7 +5054,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>411</v>
       </c>
@@ -5072,7 +5077,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>411</v>
       </c>
@@ -5095,7 +5100,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>411</v>
       </c>
@@ -5118,7 +5123,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>411</v>
       </c>
@@ -5141,7 +5146,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>411</v>
       </c>
@@ -5164,7 +5169,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>411</v>
       </c>
@@ -5187,7 +5192,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>411</v>
       </c>
@@ -5210,7 +5215,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>411</v>
       </c>
@@ -5233,7 +5238,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>411</v>
       </c>
@@ -5256,7 +5261,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>110</v>
       </c>
@@ -5279,7 +5284,7 @@
         <v>45.454545454545404</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>342</v>
       </c>
@@ -5302,7 +5307,7 @@
         <v>43.478260869565197</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>408</v>
       </c>
@@ -5325,7 +5330,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>408</v>
       </c>
@@ -5348,7 +5353,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>408</v>
       </c>
@@ -5371,7 +5376,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>408</v>
       </c>
@@ -5394,7 +5399,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>408</v>
       </c>
@@ -5417,7 +5422,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -5440,7 +5445,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>408</v>
       </c>
@@ -5463,7 +5468,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>408</v>
       </c>
@@ -5486,7 +5491,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>408</v>
       </c>
@@ -5509,7 +5514,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>408</v>
       </c>
@@ -5532,7 +5537,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>408</v>
       </c>
@@ -5555,7 +5560,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>408</v>
       </c>
@@ -5578,7 +5583,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>408</v>
       </c>
@@ -5601,7 +5606,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>408</v>
       </c>
@@ -5624,7 +5629,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>408</v>
       </c>
@@ -5647,7 +5652,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>229</v>
       </c>
@@ -5670,7 +5675,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -5693,7 +5698,7 @@
         <v>38.461538461538403</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>557</v>
       </c>
@@ -5716,7 +5721,7 @@
         <v>35.294117647058798</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>321</v>
       </c>
@@ -5739,7 +5744,7 @@
         <v>34.782608695652101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>342</v>
       </c>
@@ -5762,7 +5767,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>342</v>
       </c>
@@ -5785,7 +5790,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>342</v>
       </c>
@@ -5808,7 +5813,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>189</v>
       </c>
@@ -5831,7 +5836,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>189</v>
       </c>
@@ -5854,7 +5859,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>408</v>
       </c>
@@ -5877,7 +5882,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>453</v>
       </c>
@@ -5900,7 +5905,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>453</v>
       </c>
@@ -5923,7 +5928,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>443</v>
       </c>
@@ -5946,7 +5951,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>152</v>
       </c>
@@ -5969,7 +5974,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>57</v>
       </c>
@@ -5992,7 +5997,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>57</v>
       </c>
@@ -6015,7 +6020,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>57</v>
       </c>
@@ -6038,81 +6043,81 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="B164">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C164">
-        <v>19830.419999999998</v>
+        <v>17952.34</v>
       </c>
       <c r="D164" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="E164" t="s">
         <v>74</v>
       </c>
       <c r="F164">
-        <v>28.571428571428498</v>
+        <v>42.105263157894697</v>
       </c>
       <c r="G164">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>344</v>
-      </c>
-      <c r="B165">
-        <v>1124</v>
-      </c>
-      <c r="C165">
-        <v>19830.419999999998</v>
-      </c>
-      <c r="D165" t="s">
-        <v>345</v>
-      </c>
-      <c r="E165" t="s">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B165" s="1">
+        <v>1125</v>
+      </c>
+      <c r="C165" s="1">
+        <v>6050.17</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F165">
-        <v>28.571428571428498</v>
-      </c>
-      <c r="G165">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>344</v>
-      </c>
-      <c r="B166">
+      <c r="F165" s="1">
+        <v>100</v>
+      </c>
+      <c r="G165" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B166" s="1">
         <v>1125</v>
       </c>
-      <c r="C166">
-        <v>19830.419999999998</v>
-      </c>
-      <c r="D166" t="s">
-        <v>345</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="C166" s="1">
+        <v>6567.22</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F166">
-        <v>28.571428571428498</v>
-      </c>
-      <c r="G166">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F166" s="1">
+        <v>100</v>
+      </c>
+      <c r="G166" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>344</v>
       </c>
       <c r="B167">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C167">
         <v>19830.419999999998</v>
@@ -6130,76 +6135,76 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>344</v>
+        <v>555</v>
       </c>
       <c r="B168">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C168">
-        <v>19830.419999999998</v>
+        <v>3544.58</v>
       </c>
       <c r="D168" t="s">
-        <v>345</v>
+        <v>556</v>
       </c>
       <c r="E168" t="s">
         <v>74</v>
       </c>
       <c r="F168">
+        <v>36.363636363636303</v>
+      </c>
+      <c r="G168">
         <v>28.571428571428498</v>
       </c>
-      <c r="G168">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>344</v>
+        <v>550</v>
       </c>
       <c r="B169">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C169">
-        <v>19830.419999999998</v>
+        <v>7056.65</v>
       </c>
       <c r="D169" t="s">
-        <v>345</v>
+        <v>551</v>
       </c>
       <c r="E169" t="s">
         <v>74</v>
       </c>
       <c r="F169">
-        <v>28.571428571428498</v>
+        <v>31.578947368421002</v>
       </c>
       <c r="G169">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="B170">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="C170">
-        <v>19830.419999999998</v>
+        <v>17952.34</v>
       </c>
       <c r="D170" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="E170" t="s">
         <v>74</v>
       </c>
       <c r="F170">
-        <v>28.571428571428498</v>
+        <v>42.105263157894697</v>
       </c>
       <c r="G170">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>555</v>
       </c>
@@ -6222,7 +6227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>86</v>
       </c>
@@ -6245,7 +6250,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>339</v>
       </c>
@@ -6268,7 +6273,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>12</v>
       </c>
@@ -6291,7 +6296,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>24</v>
       </c>
@@ -6314,7 +6319,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="176" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>113</v>
       </c>
@@ -6337,7 +6342,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="177" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>113</v>
       </c>
@@ -6360,7 +6365,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="178" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>113</v>
       </c>
@@ -6383,7 +6388,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>455</v>
       </c>
@@ -6406,81 +6411,81 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>555</v>
-      </c>
-      <c r="B180">
-        <v>1122</v>
-      </c>
-      <c r="C180">
-        <v>10587.23</v>
-      </c>
-      <c r="D180" t="s">
-        <v>556</v>
-      </c>
-      <c r="E180" t="s">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B180" s="1">
+        <v>1126</v>
+      </c>
+      <c r="C180" s="1">
+        <v>6050.17</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F180">
-        <v>36.363636363636303</v>
-      </c>
-      <c r="G180">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>555</v>
-      </c>
-      <c r="B181">
-        <v>1123</v>
-      </c>
-      <c r="C181">
-        <v>3544.58</v>
-      </c>
-      <c r="D181" t="s">
-        <v>556</v>
-      </c>
-      <c r="E181" t="s">
+      <c r="F180" s="1">
+        <v>100</v>
+      </c>
+      <c r="G180" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B181" s="1">
+        <v>1126</v>
+      </c>
+      <c r="C181" s="1">
+        <v>6567.22</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F181">
-        <v>36.363636363636303</v>
-      </c>
-      <c r="G181">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F181" s="1">
+        <v>100</v>
+      </c>
+      <c r="G181" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>555</v>
+        <v>344</v>
       </c>
       <c r="B182">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C182">
-        <v>3544.58</v>
+        <v>19830.419999999998</v>
       </c>
       <c r="D182" t="s">
-        <v>556</v>
+        <v>345</v>
       </c>
       <c r="E182" t="s">
         <v>74</v>
       </c>
       <c r="F182">
-        <v>36.363636363636303</v>
+        <v>28.571428571428498</v>
       </c>
       <c r="G182">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>555</v>
       </c>
       <c r="B183">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C183">
         <v>3544.58</v>
@@ -6498,99 +6503,99 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B184">
         <v>1126</v>
       </c>
       <c r="C184">
-        <v>3544.58</v>
+        <v>7056.65</v>
       </c>
       <c r="D184" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E184" t="s">
         <v>74</v>
       </c>
       <c r="F184">
-        <v>36.363636363636303</v>
+        <v>31.578947368421002</v>
       </c>
       <c r="G184">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>555</v>
+        <v>362</v>
       </c>
       <c r="B185">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C185">
-        <v>3544.58</v>
+        <v>17952.34</v>
       </c>
       <c r="D185" t="s">
-        <v>556</v>
+        <v>363</v>
       </c>
       <c r="E185" t="s">
         <v>74</v>
       </c>
       <c r="F185">
-        <v>36.363636363636303</v>
+        <v>42.105263157894697</v>
       </c>
       <c r="G185">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>555</v>
-      </c>
-      <c r="B186">
-        <v>1128</v>
-      </c>
-      <c r="C186">
-        <v>3544.58</v>
-      </c>
-      <c r="D186" t="s">
-        <v>556</v>
-      </c>
-      <c r="E186" t="s">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A186" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B186" s="1">
+        <v>1127</v>
+      </c>
+      <c r="C186" s="1">
+        <v>6050.17</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F186">
-        <v>36.363636363636303</v>
-      </c>
-      <c r="G186">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>555</v>
-      </c>
-      <c r="B187">
-        <v>1129</v>
-      </c>
-      <c r="C187">
-        <v>3544.58</v>
-      </c>
-      <c r="D187" t="s">
-        <v>556</v>
-      </c>
-      <c r="E187" t="s">
+      <c r="F186" s="1">
+        <v>100</v>
+      </c>
+      <c r="G186" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A187" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B187" s="1">
+        <v>1127</v>
+      </c>
+      <c r="C187" s="1">
+        <v>6567.22</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F187">
-        <v>36.363636363636303</v>
-      </c>
-      <c r="G187">
-        <v>28.571428571428498</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F187" s="1">
+        <v>100</v>
+      </c>
+      <c r="G187" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>156</v>
       </c>
@@ -6613,7 +6618,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>156</v>
       </c>
@@ -6636,7 +6641,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>156</v>
       </c>
@@ -6659,7 +6664,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>156</v>
       </c>
@@ -6682,7 +6687,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>156</v>
       </c>
@@ -6705,58 +6710,58 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>550</v>
+        <v>344</v>
       </c>
       <c r="B193">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="C193">
-        <v>1164.32</v>
+        <v>19830.419999999998</v>
       </c>
       <c r="D193" t="s">
-        <v>551</v>
+        <v>345</v>
       </c>
       <c r="E193" t="s">
         <v>74</v>
       </c>
       <c r="F193">
-        <v>31.578947368421002</v>
+        <v>28.571428571428498</v>
       </c>
       <c r="G193">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B194">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C194">
-        <v>7056.65</v>
+        <v>3544.58</v>
       </c>
       <c r="D194" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E194" t="s">
         <v>74</v>
       </c>
       <c r="F194">
-        <v>31.578947368421002</v>
+        <v>36.363636363636303</v>
       </c>
       <c r="G194">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>550</v>
       </c>
       <c r="B195">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C195">
         <v>7056.65</v>
@@ -6774,122 +6779,122 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>550</v>
+        <v>362</v>
       </c>
       <c r="B196">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C196">
-        <v>7056.65</v>
+        <v>17952.34</v>
       </c>
       <c r="D196" t="s">
-        <v>551</v>
+        <v>363</v>
       </c>
       <c r="E196" t="s">
         <v>74</v>
       </c>
       <c r="F196">
-        <v>31.578947368421002</v>
+        <v>42.105263157894697</v>
       </c>
       <c r="G196">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>550</v>
-      </c>
-      <c r="B197">
-        <v>1126</v>
-      </c>
-      <c r="C197">
-        <v>7056.65</v>
-      </c>
-      <c r="D197" t="s">
-        <v>551</v>
-      </c>
-      <c r="E197" t="s">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A197" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1128</v>
+      </c>
+      <c r="C197" s="1">
+        <v>6050.17</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F197">
-        <v>31.578947368421002</v>
-      </c>
-      <c r="G197">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>550</v>
-      </c>
-      <c r="B198">
-        <v>1127</v>
-      </c>
-      <c r="C198">
-        <v>7056.65</v>
-      </c>
-      <c r="D198" t="s">
-        <v>551</v>
-      </c>
-      <c r="E198" t="s">
+      <c r="F197" s="1">
+        <v>100</v>
+      </c>
+      <c r="G197" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A198" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B198" s="1">
+        <v>1128</v>
+      </c>
+      <c r="C198" s="1">
+        <v>6567.22</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F198">
-        <v>31.578947368421002</v>
-      </c>
-      <c r="G198">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F198" s="1">
+        <v>100</v>
+      </c>
+      <c r="G198" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>550</v>
+        <v>344</v>
       </c>
       <c r="B199">
         <v>1128</v>
       </c>
       <c r="C199">
-        <v>7056.65</v>
+        <v>19830.419999999998</v>
       </c>
       <c r="D199" t="s">
-        <v>551</v>
+        <v>345</v>
       </c>
       <c r="E199" t="s">
         <v>74</v>
       </c>
       <c r="F199">
-        <v>31.578947368421002</v>
+        <v>28.571428571428498</v>
       </c>
       <c r="G199">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B200">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C200">
-        <v>7056.65</v>
+        <v>3544.58</v>
       </c>
       <c r="D200" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E200" t="s">
         <v>74</v>
       </c>
       <c r="F200">
-        <v>31.578947368421002</v>
+        <v>36.363636363636303</v>
       </c>
       <c r="G200">
-        <v>27.272727272727199</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>580</v>
       </c>
@@ -6912,7 +6917,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>580</v>
       </c>
@@ -6935,7 +6940,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>57</v>
       </c>
@@ -6958,7 +6963,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>57</v>
       </c>
@@ -6981,7 +6986,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>57</v>
       </c>
@@ -7004,7 +7009,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>57</v>
       </c>
@@ -7027,7 +7032,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>57</v>
       </c>
@@ -7050,7 +7055,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>57</v>
       </c>
@@ -7073,7 +7078,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>57</v>
       </c>
@@ -7096,7 +7101,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>57</v>
       </c>
@@ -7119,7 +7124,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>57</v>
       </c>
@@ -7142,7 +7147,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>57</v>
       </c>
@@ -7165,7 +7170,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>57</v>
       </c>
@@ -7188,7 +7193,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>57</v>
       </c>
@@ -7211,7 +7216,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>57</v>
       </c>
@@ -7234,7 +7239,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>57</v>
       </c>
@@ -7257,7 +7262,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>57</v>
       </c>
@@ -7280,7 +7285,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>447</v>
       </c>
@@ -7303,7 +7308,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -7326,7 +7331,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>95</v>
       </c>
@@ -7349,7 +7354,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>89</v>
       </c>
@@ -7372,7 +7377,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>89</v>
       </c>
@@ -7395,7 +7400,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>89</v>
       </c>
@@ -7418,7 +7423,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>464</v>
       </c>
@@ -7441,7 +7446,7 @@
         <v>25.6410256410256</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>286</v>
       </c>
@@ -7464,7 +7469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>286</v>
       </c>
@@ -7487,7 +7492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>286</v>
       </c>
@@ -7510,7 +7515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>286</v>
       </c>
@@ -7533,7 +7538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>348</v>
       </c>
@@ -7556,7 +7561,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>408</v>
       </c>
@@ -7579,7 +7584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>408</v>
       </c>
@@ -7602,7 +7607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>51</v>
       </c>
@@ -7625,7 +7630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>51</v>
       </c>
@@ -7648,7 +7653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>51</v>
       </c>
@@ -7671,7 +7676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>86</v>
       </c>
@@ -7694,7 +7699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -7717,7 +7722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>234</v>
       </c>
@@ -7740,7 +7745,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>368</v>
       </c>
@@ -7763,7 +7768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>552</v>
       </c>
@@ -7786,7 +7791,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>552</v>
       </c>
@@ -7809,7 +7814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>552</v>
       </c>
@@ -7832,7 +7837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>229</v>
       </c>
@@ -7855,7 +7860,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>229</v>
       </c>
@@ -7878,7 +7883,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>38</v>
       </c>
@@ -7901,7 +7906,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>104</v>
       </c>
@@ -7924,7 +7929,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>498</v>
       </c>
@@ -7947,7 +7952,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>498</v>
       </c>
@@ -7970,7 +7975,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>498</v>
       </c>
@@ -7993,7 +7998,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>498</v>
       </c>
@@ -8016,7 +8021,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>552</v>
       </c>
@@ -8039,7 +8044,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>435</v>
       </c>
@@ -8062,7 +8067,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>435</v>
       </c>
@@ -8085,7 +8090,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>435</v>
       </c>
@@ -8108,7 +8113,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -8131,7 +8136,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>319</v>
       </c>
@@ -8154,7 +8159,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>546</v>
       </c>
@@ -8177,7 +8182,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>546</v>
       </c>
@@ -8200,7 +8205,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>51</v>
       </c>
@@ -8223,7 +8228,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>460</v>
       </c>
@@ -8246,7 +8251,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>518</v>
       </c>
@@ -8269,7 +8274,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>113</v>
       </c>
@@ -8292,7 +8297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>411</v>
       </c>
@@ -8315,7 +8320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>192</v>
       </c>
@@ -8338,7 +8343,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>321</v>
       </c>
@@ -8361,7 +8366,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>104</v>
       </c>
@@ -8384,7 +8389,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>104</v>
       </c>
@@ -8407,7 +8412,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>550</v>
       </c>
@@ -8430,7 +8435,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>44</v>
       </c>
@@ -8453,7 +8458,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>44</v>
       </c>
@@ -8476,7 +8481,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>44</v>
       </c>
@@ -8499,35 +8504,35 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>362</v>
+        <v>550</v>
       </c>
       <c r="B271">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="C271">
-        <v>17952.34</v>
+        <v>7056.65</v>
       </c>
       <c r="D271" t="s">
-        <v>363</v>
+        <v>551</v>
       </c>
       <c r="E271" t="s">
         <v>74</v>
       </c>
       <c r="F271">
-        <v>42.105263157894697</v>
+        <v>31.578947368421002</v>
       </c>
       <c r="G271">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>362</v>
       </c>
       <c r="B272">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C272">
         <v>17952.34</v>
@@ -8545,122 +8550,122 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>362</v>
-      </c>
-      <c r="B273">
-        <v>1125</v>
-      </c>
-      <c r="C273">
-        <v>17952.34</v>
-      </c>
-      <c r="D273" t="s">
-        <v>363</v>
-      </c>
-      <c r="E273" t="s">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B273" s="1">
+        <v>1129</v>
+      </c>
+      <c r="C273" s="1">
+        <v>6050.17</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E273" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F273">
-        <v>42.105263157894697</v>
-      </c>
-      <c r="G273">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>362</v>
-      </c>
-      <c r="B274">
-        <v>1126</v>
-      </c>
-      <c r="C274">
-        <v>17952.34</v>
-      </c>
-      <c r="D274" t="s">
-        <v>363</v>
-      </c>
-      <c r="E274" t="s">
+      <c r="F273" s="1">
+        <v>100</v>
+      </c>
+      <c r="G273" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B274" s="1">
+        <v>1129</v>
+      </c>
+      <c r="C274" s="1">
+        <v>6567.22</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E274" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F274">
-        <v>42.105263157894697</v>
-      </c>
-      <c r="G274">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F274" s="1">
+        <v>100</v>
+      </c>
+      <c r="G274" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B275">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C275">
-        <v>17952.34</v>
+        <v>19830.419999999998</v>
       </c>
       <c r="D275" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="E275" t="s">
         <v>74</v>
       </c>
       <c r="F275">
-        <v>42.105263157894697</v>
+        <v>28.571428571428498</v>
       </c>
       <c r="G275">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>362</v>
+        <v>555</v>
       </c>
       <c r="B276">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C276">
-        <v>17952.34</v>
+        <v>3544.58</v>
       </c>
       <c r="D276" t="s">
-        <v>363</v>
+        <v>556</v>
       </c>
       <c r="E276" t="s">
         <v>74</v>
       </c>
       <c r="F276">
-        <v>42.105263157894697</v>
+        <v>36.363636363636303</v>
       </c>
       <c r="G276">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+        <v>28.571428571428498</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>362</v>
+        <v>550</v>
       </c>
       <c r="B277">
         <v>1129</v>
       </c>
       <c r="C277">
-        <v>17952.34</v>
+        <v>7056.65</v>
       </c>
       <c r="D277" t="s">
-        <v>363</v>
+        <v>551</v>
       </c>
       <c r="E277" t="s">
         <v>74</v>
       </c>
       <c r="F277">
-        <v>42.105263157894697</v>
+        <v>31.578947368421002</v>
       </c>
       <c r="G277">
-        <v>18.181818181818102</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27.272727272727199</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>580</v>
       </c>
@@ -8683,7 +8688,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>203</v>
       </c>
@@ -8706,7 +8711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>462</v>
       </c>
@@ -8729,7 +8734,7 @@
         <v>15.789473684210501</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>229</v>
       </c>
@@ -8752,7 +8757,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>331</v>
       </c>
@@ -8775,7 +8780,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>557</v>
       </c>
@@ -8798,7 +8803,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>580</v>
       </c>
@@ -8821,7 +8826,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>478</v>
       </c>
@@ -8844,7 +8849,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>231</v>
       </c>
@@ -8867,7 +8872,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>478</v>
       </c>
@@ -8890,7 +8895,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>136</v>
       </c>
@@ -8913,7 +8918,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>136</v>
       </c>
@@ -8936,7 +8941,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>370</v>
       </c>
@@ -8959,7 +8964,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>72</v>
       </c>
@@ -8982,7 +8987,7 @@
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>554</v>
       </c>
@@ -9005,7 +9010,7 @@
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>555</v>
       </c>
@@ -9028,7 +9033,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>411</v>
       </c>
@@ -9051,7 +9056,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>411</v>
       </c>
@@ -9074,7 +9079,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>411</v>
       </c>
@@ -9097,7 +9102,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>550</v>
       </c>
@@ -9120,7 +9125,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>119</v>
       </c>
@@ -9143,7 +9148,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>325</v>
       </c>
@@ -9166,30 +9171,30 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>557</v>
+        <v>362</v>
       </c>
       <c r="B300">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="C300">
-        <v>17605.02</v>
+        <v>17952.34</v>
       </c>
       <c r="D300" t="s">
-        <v>558</v>
+        <v>363</v>
       </c>
       <c r="E300" t="s">
         <v>74</v>
       </c>
       <c r="F300">
-        <v>25</v>
+        <v>42.105263157894697</v>
       </c>
       <c r="G300">
-        <v>11.1111111111111</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.181818181818102</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>78</v>
       </c>
@@ -9212,7 +9217,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>557</v>
       </c>
@@ -9235,7 +9240,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>557</v>
       </c>
@@ -9258,7 +9263,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>557</v>
       </c>
@@ -9281,7 +9286,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>557</v>
       </c>
@@ -9304,7 +9309,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>557</v>
       </c>
@@ -9327,7 +9332,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>119</v>
       </c>
@@ -9350,7 +9355,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>119</v>
       </c>
@@ -9373,7 +9378,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>12</v>
       </c>
@@ -9396,7 +9401,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>12</v>
       </c>
@@ -9419,7 +9424,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>516</v>
       </c>
@@ -9442,7 +9447,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>7</v>
       </c>
@@ -9465,7 +9470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>72</v>
       </c>
@@ -9488,7 +9493,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>554</v>
       </c>
@@ -9511,7 +9516,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>44</v>
       </c>
@@ -9534,7 +9539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>44</v>
       </c>
@@ -9557,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>314</v>
       </c>
@@ -9580,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>314</v>
       </c>
@@ -9603,7 +9608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>331</v>
       </c>
@@ -9626,7 +9631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>115</v>
       </c>
@@ -9634,7 +9639,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>117</v>
       </c>
@@ -9642,7 +9647,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>122</v>
       </c>
@@ -9650,7 +9655,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>126</v>
       </c>
@@ -9658,7 +9663,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>128</v>
       </c>
@@ -9666,7 +9671,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>130</v>
       </c>
@@ -9674,7 +9679,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>132</v>
       </c>
@@ -9682,7 +9687,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>134</v>
       </c>
@@ -9690,7 +9695,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>138</v>
       </c>
@@ -9698,7 +9703,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>140</v>
       </c>
@@ -9706,7 +9711,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>142</v>
       </c>
@@ -9714,7 +9719,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>144</v>
       </c>
@@ -9722,7 +9727,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>146</v>
       </c>
@@ -9730,7 +9735,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>148</v>
       </c>
@@ -9738,7 +9743,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>154</v>
       </c>
@@ -9746,7 +9751,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>158</v>
       </c>
@@ -9754,7 +9759,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>160</v>
       </c>
@@ -9762,7 +9767,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>162</v>
       </c>
@@ -9770,7 +9775,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>164</v>
       </c>
@@ -9778,7 +9783,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>166</v>
       </c>
@@ -9786,7 +9791,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>169</v>
       </c>
@@ -9794,7 +9799,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>171</v>
       </c>
@@ -9802,7 +9807,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>173</v>
       </c>
@@ -9810,7 +9815,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>175</v>
       </c>
@@ -9818,7 +9823,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>177</v>
       </c>
@@ -9826,7 +9831,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>179</v>
       </c>
@@ -9834,7 +9839,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>181</v>
       </c>
@@ -9842,7 +9847,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>183</v>
       </c>
@@ -9850,7 +9855,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>185</v>
       </c>
@@ -9858,7 +9863,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>187</v>
       </c>
@@ -9866,7 +9871,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>195</v>
       </c>
@@ -9874,7 +9879,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>197</v>
       </c>
@@ -9882,7 +9887,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>199</v>
       </c>
@@ -9890,7 +9895,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>201</v>
       </c>
@@ -9898,7 +9903,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>205</v>
       </c>
@@ -9906,7 +9911,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>207</v>
       </c>
@@ -9914,7 +9919,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>209</v>
       </c>
@@ -9922,7 +9927,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>211</v>
       </c>
@@ -9930,7 +9935,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>213</v>
       </c>
@@ -9938,7 +9943,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>215</v>
       </c>
@@ -9946,7 +9951,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>217</v>
       </c>
@@ -9954,7 +9959,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>219</v>
       </c>
@@ -9962,7 +9967,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>221</v>
       </c>
@@ -9970,7 +9975,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>223</v>
       </c>
@@ -9978,7 +9983,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>225</v>
       </c>
@@ -9986,7 +9991,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>227</v>
       </c>
@@ -9994,7 +9999,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>236</v>
       </c>
@@ -10002,7 +10007,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>238</v>
       </c>
@@ -10010,7 +10015,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>240</v>
       </c>
@@ -10018,7 +10023,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>242</v>
       </c>
@@ -10026,7 +10031,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>244</v>
       </c>
@@ -10034,7 +10039,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>246</v>
       </c>
@@ -10042,7 +10047,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>248</v>
       </c>
@@ -10050,7 +10055,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>250</v>
       </c>
@@ -10058,7 +10063,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>252</v>
       </c>
@@ -10066,7 +10071,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>254</v>
       </c>
@@ -10074,7 +10079,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>256</v>
       </c>
@@ -10082,7 +10087,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>258</v>
       </c>
@@ -10090,7 +10095,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>260</v>
       </c>
@@ -10098,7 +10103,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>262</v>
       </c>
@@ -10106,7 +10111,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>264</v>
       </c>
@@ -10114,7 +10119,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>266</v>
       </c>
@@ -10122,7 +10127,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>268</v>
       </c>
@@ -10130,7 +10135,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>270</v>
       </c>
@@ -10138,7 +10143,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>272</v>
       </c>
@@ -10146,7 +10151,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>274</v>
       </c>
@@ -10154,7 +10159,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>276</v>
       </c>
@@ -10162,7 +10167,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>278</v>
       </c>
@@ -10170,7 +10175,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>280</v>
       </c>
@@ -10178,7 +10183,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>282</v>
       </c>
@@ -10186,7 +10191,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>284</v>
       </c>
@@ -10194,7 +10199,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>289</v>
       </c>
@@ -10202,7 +10207,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>292</v>
       </c>
@@ -10210,7 +10215,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>296</v>
       </c>
@@ -10218,7 +10223,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>298</v>
       </c>
@@ -10226,7 +10231,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>300</v>
       </c>
@@ -10234,7 +10239,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>302</v>
       </c>
@@ -10242,7 +10247,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>304</v>
       </c>
@@ -10250,7 +10255,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>306</v>
       </c>
@@ -10258,7 +10263,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>308</v>
       </c>
@@ -10266,7 +10271,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>310</v>
       </c>
@@ -10274,7 +10279,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>312</v>
       </c>
@@ -10282,7 +10287,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>317</v>
       </c>
@@ -10290,7 +10295,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>323</v>
       </c>
@@ -10298,7 +10303,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>327</v>
       </c>
@@ -10306,7 +10311,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>329</v>
       </c>
@@ -10314,7 +10319,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>333</v>
       </c>
@@ -10322,7 +10327,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>335</v>
       </c>
@@ -10330,7 +10335,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>337</v>
       </c>
@@ -10338,7 +10343,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>346</v>
       </c>
@@ -10346,7 +10351,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>350</v>
       </c>
@@ -10354,7 +10359,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>352</v>
       </c>
@@ -10362,7 +10367,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>354</v>
       </c>
@@ -10370,7 +10375,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>356</v>
       </c>
@@ -10378,7 +10383,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>358</v>
       </c>
@@ -10386,7 +10391,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>360</v>
       </c>
@@ -10394,7 +10399,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>364</v>
       </c>
@@ -10402,7 +10407,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>366</v>
       </c>
@@ -10410,7 +10415,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>372</v>
       </c>
@@ -10418,7 +10423,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>374</v>
       </c>
@@ -10426,7 +10431,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>376</v>
       </c>
@@ -10434,7 +10439,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>378</v>
       </c>
@@ -10442,7 +10447,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>380</v>
       </c>
@@ -10450,7 +10455,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>382</v>
       </c>
@@ -10458,7 +10463,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>384</v>
       </c>
@@ -10466,7 +10471,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>386</v>
       </c>
@@ -10474,7 +10479,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>388</v>
       </c>
@@ -10482,7 +10487,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>390</v>
       </c>
@@ -10490,7 +10495,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>392</v>
       </c>
@@ -10498,7 +10503,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>394</v>
       </c>
@@ -10506,7 +10511,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>396</v>
       </c>
@@ -10514,7 +10519,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>398</v>
       </c>
@@ -10522,7 +10527,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>400</v>
       </c>
@@ -10530,7 +10535,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>402</v>
       </c>
@@ -10538,7 +10543,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>404</v>
       </c>
@@ -10546,7 +10551,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>406</v>
       </c>
@@ -10554,7 +10559,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>413</v>
       </c>
@@ -10562,7 +10567,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>415</v>
       </c>
@@ -10570,7 +10575,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>417</v>
       </c>
@@ -10578,7 +10583,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>419</v>
       </c>
@@ -10586,7 +10591,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>421</v>
       </c>
@@ -10594,7 +10599,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>423</v>
       </c>
@@ -10602,7 +10607,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>425</v>
       </c>
@@ -10610,7 +10615,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>427</v>
       </c>
@@ -10618,7 +10623,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>429</v>
       </c>
@@ -10626,7 +10631,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>431</v>
       </c>
@@ -10634,7 +10639,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>433</v>
       </c>
@@ -10642,7 +10647,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>441</v>
       </c>
@@ -10650,7 +10655,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>445</v>
       </c>
@@ -10658,7 +10663,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>449</v>
       </c>
@@ -10666,7 +10671,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>451</v>
       </c>
@@ -10674,7 +10679,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>458</v>
       </c>
@@ -10682,7 +10687,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>466</v>
       </c>
@@ -10690,7 +10695,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>468</v>
       </c>
@@ -10698,7 +10703,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>470</v>
       </c>
@@ -10706,7 +10711,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>472</v>
       </c>
@@ -10714,7 +10719,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>474</v>
       </c>
@@ -10722,7 +10727,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>476</v>
       </c>
@@ -10730,7 +10735,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>480</v>
       </c>
@@ -10738,7 +10743,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>482</v>
       </c>
@@ -10746,7 +10751,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>484</v>
       </c>
@@ -10754,7 +10759,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>486</v>
       </c>
@@ -10762,7 +10767,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>488</v>
       </c>
@@ -10770,7 +10775,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>490</v>
       </c>
@@ -10778,7 +10783,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>492</v>
       </c>
@@ -10786,7 +10791,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>494</v>
       </c>
@@ -10794,7 +10799,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>496</v>
       </c>
@@ -10802,7 +10807,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>500</v>
       </c>
@@ -10810,7 +10815,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>502</v>
       </c>
@@ -10818,7 +10823,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>504</v>
       </c>
@@ -10826,7 +10831,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>506</v>
       </c>
@@ -10834,7 +10839,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>508</v>
       </c>
@@ -10842,7 +10847,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>510</v>
       </c>
@@ -10850,7 +10855,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>512</v>
       </c>
@@ -10858,7 +10863,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>514</v>
       </c>
@@ -10866,7 +10871,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>520</v>
       </c>
@@ -10874,7 +10879,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>522</v>
       </c>
@@ -10882,7 +10887,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>524</v>
       </c>
@@ -10890,7 +10895,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>526</v>
       </c>
@@ -10898,7 +10903,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>528</v>
       </c>
@@ -10906,7 +10911,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>530</v>
       </c>
@@ -10914,7 +10919,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>532</v>
       </c>
@@ -10922,7 +10927,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>534</v>
       </c>
@@ -10930,7 +10935,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>536</v>
       </c>
@@ -10938,7 +10943,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>538</v>
       </c>
@@ -10946,7 +10951,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>540</v>
       </c>
@@ -10954,7 +10959,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>542</v>
       </c>
@@ -10962,7 +10967,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>544</v>
       </c>
@@ -10970,7 +10975,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>548</v>
       </c>
@@ -10978,7 +10983,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>559</v>
       </c>
@@ -10986,7 +10991,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>561</v>
       </c>
@@ -10994,7 +10999,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>564</v>
       </c>
@@ -11002,7 +11007,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>566</v>
       </c>
@@ -11010,7 +11015,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>568</v>
       </c>
@@ -11018,7 +11023,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>570</v>
       </c>
@@ -11026,7 +11031,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>572</v>
       </c>
@@ -11034,7 +11039,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>574</v>
       </c>
@@ -11042,7 +11047,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>576</v>
       </c>
@@ -11050,7 +11055,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>578</v>
       </c>
@@ -11058,7 +11063,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>582</v>
       </c>
@@ -11066,7 +11071,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>584</v>
       </c>
@@ -11074,7 +11079,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>586</v>
       </c>
@@ -11082,7 +11087,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>588</v>
       </c>
@@ -11090,7 +11095,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>590</v>
       </c>
@@ -11098,7 +11103,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B504">
         <v>25</v>
       </c>
@@ -11106,7 +11111,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B505">
         <v>26</v>
       </c>
@@ -11114,7 +11119,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B506">
         <v>30</v>
       </c>
@@ -11122,7 +11127,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B507">
         <v>31</v>
       </c>
@@ -11130,7 +11135,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B508">
         <v>32</v>
       </c>
@@ -11138,7 +11143,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B509">
         <v>33</v>
       </c>
@@ -11146,7 +11151,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B510">
         <v>219</v>
       </c>
@@ -11154,7 +11159,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B511">
         <v>220</v>
       </c>
@@ -11162,7 +11167,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B512">
         <v>223</v>
       </c>
@@ -11170,7 +11175,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="513" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B513">
         <v>224</v>
       </c>
@@ -11178,7 +11183,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="514" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B514">
         <v>227</v>
       </c>
@@ -11186,7 +11191,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="515" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B515">
         <v>228</v>
       </c>
@@ -11194,7 +11199,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="516" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B516">
         <v>229</v>
       </c>
@@ -11202,7 +11207,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="517" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B517">
         <v>230</v>
       </c>
@@ -11210,7 +11215,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="518" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B518">
         <v>232</v>
       </c>
@@ -11218,7 +11223,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="519" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B519">
         <v>233</v>
       </c>
@@ -11226,7 +11231,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="520" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B520">
         <v>589</v>
       </c>
@@ -11234,7 +11239,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="521" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B521">
         <v>590</v>
       </c>
@@ -11242,7 +11247,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="522" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B522">
         <v>591</v>
       </c>
@@ -11250,7 +11255,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="523" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B523">
         <v>592</v>
       </c>
@@ -11258,7 +11263,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="524" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B524">
         <v>593</v>
       </c>
@@ -11266,7 +11271,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="525" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B525">
         <v>594</v>
       </c>
@@ -11274,7 +11279,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="526" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B526">
         <v>595</v>
       </c>
@@ -11282,7 +11287,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="527" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B527">
         <v>596</v>
       </c>
@@ -11290,7 +11295,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="528" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B528">
         <v>597</v>
       </c>
@@ -11298,7 +11303,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="529" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B529">
         <v>598</v>
       </c>
@@ -11306,7 +11311,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="530" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B530">
         <v>607</v>
       </c>
@@ -11314,7 +11319,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="531" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B531">
         <v>614</v>
       </c>
@@ -11322,7 +11327,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="532" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B532">
         <v>644</v>
       </c>
@@ -11330,7 +11335,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="533" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B533">
         <v>712</v>
       </c>
@@ -11338,7 +11343,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="534" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B534">
         <v>713</v>
       </c>
@@ -11346,7 +11351,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="535" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B535">
         <v>714</v>
       </c>
@@ -11354,7 +11359,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="536" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B536">
         <v>715</v>
       </c>
@@ -11362,7 +11367,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="537" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B537">
         <v>710</v>
       </c>
@@ -11370,7 +11375,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="538" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B538">
         <v>711</v>
       </c>
@@ -11378,7 +11383,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="539" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B539">
         <v>708</v>
       </c>
@@ -11386,7 +11391,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="540" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B540">
         <v>709</v>
       </c>
@@ -11394,7 +11399,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="541" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B541">
         <v>1034</v>
       </c>
@@ -11402,7 +11407,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="542" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B542">
         <v>1545</v>
       </c>
@@ -11410,7 +11415,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="543" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B543">
         <v>1546</v>
       </c>
@@ -11418,7 +11423,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="544" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B544">
         <v>655</v>
       </c>
@@ -11426,7 +11431,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="545" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B545">
         <v>657</v>
       </c>
@@ -11434,7 +11439,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="546" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B546">
         <v>1672</v>
       </c>
@@ -11442,7 +11447,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="547" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B547">
         <v>900</v>
       </c>
@@ -11450,7 +11455,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="548" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B548">
         <v>901</v>
       </c>
@@ -11458,7 +11463,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="549" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B549">
         <v>902</v>
       </c>
@@ -11466,7 +11471,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="550" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B550">
         <v>903</v>
       </c>
@@ -11474,7 +11479,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="551" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B551">
         <v>1046</v>
       </c>
@@ -11482,7 +11487,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="552" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B552">
         <v>1870</v>
       </c>
@@ -11490,7 +11495,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="553" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B553">
         <v>1884</v>
       </c>
@@ -11498,7 +11503,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="554" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B554">
         <v>1892</v>
       </c>
@@ -11506,7 +11511,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="555" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B555">
         <v>1893</v>
       </c>
@@ -11514,7 +11519,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="556" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B556">
         <v>1894</v>
       </c>
@@ -11522,7 +11527,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="557" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B557">
         <v>1895</v>
       </c>
@@ -11530,7 +11535,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="558" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B558">
         <v>1330</v>
       </c>
@@ -11538,7 +11543,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="559" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B559">
         <v>1166</v>
       </c>
@@ -11546,7 +11551,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="560" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B560">
         <v>1167</v>
       </c>
@@ -11554,7 +11559,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="561" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B561">
         <v>1168</v>
       </c>
@@ -11562,7 +11567,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="562" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B562">
         <v>381</v>
       </c>
@@ -11570,7 +11575,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="563" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B563">
         <v>705</v>
       </c>
@@ -11578,7 +11583,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="564" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B564">
         <v>706</v>
       </c>
@@ -11586,7 +11591,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="565" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B565">
         <v>707</v>
       </c>
@@ -11594,7 +11599,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="566" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B566">
         <v>1292</v>
       </c>
@@ -11602,7 +11607,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="567" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B567">
         <v>1293</v>
       </c>
@@ -11610,7 +11615,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="568" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B568">
         <v>1294</v>
       </c>
@@ -11618,7 +11623,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="569" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B569">
         <v>1296</v>
       </c>
@@ -11626,7 +11631,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="570" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B570">
         <v>1297</v>
       </c>
@@ -11634,7 +11639,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="571" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B571">
         <v>1298</v>
       </c>
@@ -11642,7 +11647,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="572" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B572">
         <v>1299</v>
       </c>
@@ -11650,7 +11655,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="573" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B573">
         <v>1300</v>
       </c>
@@ -11658,7 +11663,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="574" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B574">
         <v>1301</v>
       </c>
@@ -11666,7 +11671,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="575" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B575">
         <v>1303</v>
       </c>
@@ -11674,7 +11679,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="576" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B576">
         <v>1304</v>
       </c>
@@ -11682,7 +11687,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="577" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B577">
         <v>1305</v>
       </c>
@@ -11690,7 +11695,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="578" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B578">
         <v>1306</v>
       </c>
@@ -11698,7 +11703,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="579" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B579">
         <v>1307</v>
       </c>
@@ -11706,7 +11711,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="580" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B580">
         <v>1308</v>
       </c>
@@ -11714,7 +11719,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="581" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B581">
         <v>1318</v>
       </c>
@@ -11722,7 +11727,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="582" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B582">
         <v>1320</v>
       </c>
@@ -11730,7 +11735,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="583" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B583">
         <v>1321</v>
       </c>
@@ -11738,7 +11743,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="584" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B584">
         <v>1323</v>
       </c>
@@ -11746,7 +11751,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="585" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B585">
         <v>1324</v>
       </c>
@@ -11754,7 +11759,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="586" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B586">
         <v>1325</v>
       </c>
@@ -11762,7 +11767,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="587" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B587">
         <v>1326</v>
       </c>
@@ -11770,7 +11775,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="588" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B588">
         <v>1327</v>
       </c>
@@ -11778,7 +11783,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="589" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B589">
         <v>1328</v>
       </c>
@@ -11786,7 +11791,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="590" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B590">
         <v>829</v>
       </c>
@@ -11794,7 +11799,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="591" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B591">
         <v>830</v>
       </c>
@@ -11802,7 +11807,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="592" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B592">
         <v>1505</v>
       </c>
@@ -11810,7 +11815,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="593" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B593">
         <v>696</v>
       </c>
@@ -11818,7 +11823,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="594" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B594">
         <v>697</v>
       </c>
@@ -11826,7 +11831,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="595" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B595">
         <v>700</v>
       </c>
@@ -11834,7 +11839,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="596" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B596">
         <v>701</v>
       </c>
@@ -11842,7 +11847,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="597" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B597">
         <v>702</v>
       </c>
@@ -11850,7 +11855,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="598" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B598">
         <v>703</v>
       </c>
@@ -11858,7 +11863,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="599" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B599">
         <v>704</v>
       </c>
@@ -11868,8 +11873,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G599" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G599">
-      <sortCondition descending="1" ref="G1"/>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="1122"/>
+        <filter val="1123"/>
+        <filter val="1124"/>
+        <filter val="1125"/>
+        <filter val="1126"/>
+        <filter val="1127"/>
+        <filter val="1128"/>
+        <filter val="1129"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A70:G300">
+      <sortCondition ref="B1:B599"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11878,807 +11895,747 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE894E2E-0757-442A-BA48-6351426611A7}">
-  <dimension ref="A1:B99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B91"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>194</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>225</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>226</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>375</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>456</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>457</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>716</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>717</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>718</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>719</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>720</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>738</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>739</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>740</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>744</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>745</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>746</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>826</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>827</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>1115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1116</v>
+      </c>
+      <c r="B32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1120</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1121</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1123</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1124</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1125</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1128</v>
+      </c>
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1129</v>
+      </c>
+      <c r="B43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>1243</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1309</v>
+      </c>
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1310</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1311</v>
+      </c>
+      <c r="B47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1312</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>1319</v>
+      </c>
+      <c r="B49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1344</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1346</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>1416</v>
+      </c>
+      <c r="B52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1436</v>
+      </c>
+      <c r="B53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1508</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>1509</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56">
         <v>1524</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B56" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>1652</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>1653</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>1654</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>1655</v>
+      </c>
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61">
         <v>1656</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B61" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62">
         <v>1657</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B62" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63">
         <v>1658</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B63" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64">
         <v>1659</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B64" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
         <v>1660</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B65" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>1652</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>1653</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>1654</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>1655</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>194</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>1344</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>1346</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>827</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>826</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>1677</v>
+      </c>
+      <c r="B66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>1685</v>
+      </c>
+      <c r="B67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>1686</v>
+      </c>
+      <c r="B68" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>1687</v>
+      </c>
+      <c r="B69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>1767</v>
+      </c>
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>1768</v>
+      </c>
+      <c r="B71" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>1868</v>
+      </c>
+      <c r="B72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>1869</v>
+      </c>
+      <c r="B73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>1871</v>
+      </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>1872</v>
+      </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>1873</v>
+      </c>
+      <c r="B76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>1874</v>
+      </c>
+      <c r="B77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>1875</v>
+      </c>
+      <c r="B78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>1876</v>
+      </c>
+      <c r="B79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>1877</v>
+      </c>
+      <c r="B80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>1878</v>
+      </c>
+      <c r="B81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>1879</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>1880</v>
+      </c>
+      <c r="B83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>1881</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>1882</v>
+      </c>
+      <c r="B85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>1883</v>
+      </c>
+      <c r="B86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87">
         <v>1885</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B87" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88">
         <v>1886</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B88" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89">
         <v>1887</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B89" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90">
         <v>1888</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B90" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>716</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>717</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>718</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>719</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>720</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>746</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>1117</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>1677</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>1685</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>1686</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>1687</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91">
         <v>1890</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B91" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>1868</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>1869</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>1871</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>1872</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>1873</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>1874</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>1875</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>1876</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>1877</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>1878</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>1879</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>1880</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
-        <v>1881</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>1882</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>1883</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>1319</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>1436</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>456</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
-        <v>457</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
-        <v>375</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
-        <v>225</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
-        <v>226</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
-        <v>1508</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
-        <v>1509</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
-        <v>1767</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
-        <v>1768</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
-        <v>1309</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
-        <v>1310</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
-        <v>1311</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
-        <v>1312</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
-        <v>1122</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>1123</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>1124</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>1125</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>1126</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
-        <v>1127</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
-        <v>1128</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <v>1129</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
-        <v>1122</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
-        <v>1123</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
-        <v>1124</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
-        <v>1125</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>1126</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>1127</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>1128</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>1129</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>1120</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>1121</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>1116</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>1115</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>28</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>29</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>23</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>24</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>744</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>745</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>1416</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <v>738</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>739</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>740</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:B91" xr:uid="{BE894E2E-0757-442A-BA48-6351426611A7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B91">
+      <sortCondition ref="A1:A91"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Mappings/mapping_tailing.xlsx
+++ b/data/Mappings/mapping_tailing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1193B88A-7CFB-4AB9-AFF7-900DABFD721F}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72C55137-DDDF-4E4F-8C89-67A59360918C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LT" sheetId="1" r:id="rId1"/>
@@ -2281,7 +2281,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G599"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2317,7 +2316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2340,7 +2339,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2501,7 +2500,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2547,7 +2546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -2616,7 +2615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
@@ -2869,7 +2868,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -2938,7 +2937,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -2984,7 +2983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -3007,7 +3006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -3053,7 +3052,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -3099,7 +3098,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
@@ -3145,7 +3144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -3168,7 +3167,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
@@ -3191,7 +3190,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
@@ -3214,7 +3213,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>51</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>51</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3352,7 +3351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
@@ -3421,7 +3420,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -3444,7 +3443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -3467,7 +3466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -3490,7 +3489,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -3513,7 +3512,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -3536,7 +3535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>59</v>
       </c>
@@ -3605,7 +3604,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -3674,7 +3673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>63</v>
       </c>
@@ -3697,7 +3696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>66</v>
       </c>
@@ -3720,7 +3719,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>66</v>
       </c>
@@ -3766,7 +3765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>69</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -3858,7 +3857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
@@ -4249,7 +4248,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="86" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4272,7 +4271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4295,7 +4294,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>78</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>80</v>
       </c>
@@ -4341,7 +4340,7 @@
         <v>91.6666666666666</v>
       </c>
     </row>
-    <row r="90" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>83</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>83</v>
       </c>
@@ -4387,7 +4386,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>86</v>
       </c>
@@ -4410,7 +4409,7 @@
         <v>85.714285714285694</v>
       </c>
     </row>
-    <row r="93" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>86</v>
       </c>
@@ -4433,7 +4432,7 @@
         <v>85.714285714285694</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>89</v>
       </c>
@@ -4456,7 +4455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>89</v>
       </c>
@@ -4479,7 +4478,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>92</v>
       </c>
@@ -4502,7 +4501,7 @@
         <v>76.923076923076906</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -4525,7 +4524,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>95</v>
       </c>
@@ -4548,7 +4547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>95</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>319</v>
       </c>
@@ -4594,7 +4593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>325</v>
       </c>
@@ -4617,7 +4616,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>98</v>
       </c>
@@ -4640,7 +4639,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -4663,7 +4662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -4686,7 +4685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>438</v>
       </c>
@@ -4709,7 +4708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -4732,7 +4731,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -4755,7 +4754,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -4778,7 +4777,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -4801,7 +4800,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -4824,7 +4823,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>107</v>
       </c>
@@ -4847,7 +4846,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>107</v>
       </c>
@@ -4870,7 +4869,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>107</v>
       </c>
@@ -4893,7 +4892,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>107</v>
       </c>
@@ -4916,7 +4915,7 @@
         <v>48.484848484848399</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>411</v>
       </c>
@@ -4939,7 +4938,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>411</v>
       </c>
@@ -4962,7 +4961,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>411</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>411</v>
       </c>
@@ -5008,7 +5007,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>411</v>
       </c>
@@ -5031,7 +5030,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>411</v>
       </c>
@@ -5054,7 +5053,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>411</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>411</v>
       </c>
@@ -5100,7 +5099,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>411</v>
       </c>
@@ -5123,7 +5122,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>411</v>
       </c>
@@ -5146,7 +5145,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>411</v>
       </c>
@@ -5169,7 +5168,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>411</v>
       </c>
@@ -5192,7 +5191,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>411</v>
       </c>
@@ -5215,7 +5214,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>411</v>
       </c>
@@ -5238,7 +5237,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>411</v>
       </c>
@@ -5261,7 +5260,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>110</v>
       </c>
@@ -5284,7 +5283,7 @@
         <v>45.454545454545404</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>342</v>
       </c>
@@ -5307,7 +5306,7 @@
         <v>43.478260869565197</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>408</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>408</v>
       </c>
@@ -5353,7 +5352,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>408</v>
       </c>
@@ -5376,7 +5375,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>408</v>
       </c>
@@ -5399,7 +5398,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>408</v>
       </c>
@@ -5422,7 +5421,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -5445,7 +5444,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>408</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>408</v>
       </c>
@@ -5491,7 +5490,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>408</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>408</v>
       </c>
@@ -5537,7 +5536,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>408</v>
       </c>
@@ -5560,7 +5559,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>408</v>
       </c>
@@ -5583,7 +5582,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>408</v>
       </c>
@@ -5606,7 +5605,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>408</v>
       </c>
@@ -5629,7 +5628,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>408</v>
       </c>
@@ -5652,7 +5651,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>229</v>
       </c>
@@ -5675,7 +5674,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -5698,7 +5697,7 @@
         <v>38.461538461538403</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>557</v>
       </c>
@@ -5721,7 +5720,7 @@
         <v>35.294117647058798</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>321</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>34.782608695652101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>342</v>
       </c>
@@ -5767,7 +5766,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>342</v>
       </c>
@@ -5790,7 +5789,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>342</v>
       </c>
@@ -5813,7 +5812,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>189</v>
       </c>
@@ -5836,7 +5835,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>189</v>
       </c>
@@ -5859,7 +5858,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>408</v>
       </c>
@@ -5882,7 +5881,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>453</v>
       </c>
@@ -5905,7 +5904,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>453</v>
       </c>
@@ -5928,7 +5927,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>443</v>
       </c>
@@ -5951,7 +5950,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>152</v>
       </c>
@@ -5974,7 +5973,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>57</v>
       </c>
@@ -5997,7 +5996,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>57</v>
       </c>
@@ -6020,7 +6019,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>57</v>
       </c>
@@ -6204,7 +6203,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>555</v>
       </c>
@@ -6227,7 +6226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>86</v>
       </c>
@@ -6250,7 +6249,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>339</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>12</v>
       </c>
@@ -6296,7 +6295,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>24</v>
       </c>
@@ -6319,7 +6318,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="176" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>113</v>
       </c>
@@ -6342,7 +6341,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="177" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>113</v>
       </c>
@@ -6365,7 +6364,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="178" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>113</v>
       </c>
@@ -6388,7 +6387,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>455</v>
       </c>
@@ -6595,7 +6594,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>156</v>
       </c>
@@ -6618,7 +6617,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>156</v>
       </c>
@@ -6641,7 +6640,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>156</v>
       </c>
@@ -6664,7 +6663,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>156</v>
       </c>
@@ -6687,7 +6686,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>156</v>
       </c>
@@ -6894,7 +6893,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>580</v>
       </c>
@@ -6917,7 +6916,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>580</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>57</v>
       </c>
@@ -6963,7 +6962,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>57</v>
       </c>
@@ -6986,7 +6985,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>57</v>
       </c>
@@ -7009,7 +7008,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>57</v>
       </c>
@@ -7032,7 +7031,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>57</v>
       </c>
@@ -7055,7 +7054,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>57</v>
       </c>
@@ -7078,7 +7077,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>57</v>
       </c>
@@ -7101,7 +7100,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>57</v>
       </c>
@@ -7124,7 +7123,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>57</v>
       </c>
@@ -7147,7 +7146,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>57</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>57</v>
       </c>
@@ -7193,7 +7192,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>57</v>
       </c>
@@ -7216,7 +7215,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>57</v>
       </c>
@@ -7239,7 +7238,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>57</v>
       </c>
@@ -7262,7 +7261,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>57</v>
       </c>
@@ -7285,7 +7284,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>447</v>
       </c>
@@ -7308,7 +7307,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -7331,7 +7330,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>95</v>
       </c>
@@ -7354,7 +7353,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>89</v>
       </c>
@@ -7377,7 +7376,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>89</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>89</v>
       </c>
@@ -7423,7 +7422,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>464</v>
       </c>
@@ -7446,7 +7445,7 @@
         <v>25.6410256410256</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>286</v>
       </c>
@@ -7469,7 +7468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>286</v>
       </c>
@@ -7492,7 +7491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>286</v>
       </c>
@@ -7515,7 +7514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>286</v>
       </c>
@@ -7538,7 +7537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>348</v>
       </c>
@@ -7561,7 +7560,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>408</v>
       </c>
@@ -7584,7 +7583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>408</v>
       </c>
@@ -7607,7 +7606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>51</v>
       </c>
@@ -7630,7 +7629,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>51</v>
       </c>
@@ -7653,7 +7652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>51</v>
       </c>
@@ -7676,7 +7675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>86</v>
       </c>
@@ -7699,7 +7698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -7722,7 +7721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>234</v>
       </c>
@@ -7745,7 +7744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>368</v>
       </c>
@@ -7768,7 +7767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>552</v>
       </c>
@@ -7791,7 +7790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>552</v>
       </c>
@@ -7814,7 +7813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>552</v>
       </c>
@@ -7837,7 +7836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>229</v>
       </c>
@@ -7860,7 +7859,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>229</v>
       </c>
@@ -7883,7 +7882,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>38</v>
       </c>
@@ -7906,7 +7905,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>104</v>
       </c>
@@ -7929,7 +7928,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>498</v>
       </c>
@@ -7952,7 +7951,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>498</v>
       </c>
@@ -7975,7 +7974,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>498</v>
       </c>
@@ -7998,7 +7997,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>498</v>
       </c>
@@ -8021,7 +8020,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>552</v>
       </c>
@@ -8044,7 +8043,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>435</v>
       </c>
@@ -8067,7 +8066,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>435</v>
       </c>
@@ -8090,7 +8089,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>435</v>
       </c>
@@ -8113,7 +8112,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -8136,7 +8135,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>319</v>
       </c>
@@ -8159,7 +8158,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>546</v>
       </c>
@@ -8182,7 +8181,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>546</v>
       </c>
@@ -8205,7 +8204,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>51</v>
       </c>
@@ -8228,7 +8227,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>460</v>
       </c>
@@ -8251,7 +8250,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>518</v>
       </c>
@@ -8274,7 +8273,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>113</v>
       </c>
@@ -8297,7 +8296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>411</v>
       </c>
@@ -8320,7 +8319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>192</v>
       </c>
@@ -8343,7 +8342,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>321</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>104</v>
       </c>
@@ -8389,7 +8388,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>104</v>
       </c>
@@ -8412,7 +8411,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>550</v>
       </c>
@@ -8435,7 +8434,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>44</v>
       </c>
@@ -8458,7 +8457,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>44</v>
       </c>
@@ -8481,7 +8480,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>44</v>
       </c>
@@ -8665,7 +8664,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>580</v>
       </c>
@@ -8688,7 +8687,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>203</v>
       </c>
@@ -8711,7 +8710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>462</v>
       </c>
@@ -8734,7 +8733,7 @@
         <v>15.789473684210501</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>229</v>
       </c>
@@ -8757,7 +8756,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>331</v>
       </c>
@@ -8780,7 +8779,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>557</v>
       </c>
@@ -8803,7 +8802,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>580</v>
       </c>
@@ -8826,7 +8825,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>478</v>
       </c>
@@ -8849,7 +8848,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>231</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>478</v>
       </c>
@@ -8895,7 +8894,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>136</v>
       </c>
@@ -8918,7 +8917,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>136</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>370</v>
       </c>
@@ -8964,7 +8963,7 @@
         <v>13.3333333333333</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>72</v>
       </c>
@@ -8987,7 +8986,7 @@
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>554</v>
       </c>
@@ -9010,7 +9009,7 @@
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>555</v>
       </c>
@@ -9033,7 +9032,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>411</v>
       </c>
@@ -9056,7 +9055,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>411</v>
       </c>
@@ -9079,7 +9078,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>411</v>
       </c>
@@ -9102,7 +9101,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>550</v>
       </c>
@@ -9125,7 +9124,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>119</v>
       </c>
@@ -9148,7 +9147,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>325</v>
       </c>
@@ -9194,7 +9193,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>78</v>
       </c>
@@ -9217,7 +9216,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>557</v>
       </c>
@@ -9240,7 +9239,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>557</v>
       </c>
@@ -9263,7 +9262,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>557</v>
       </c>
@@ -9286,7 +9285,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>557</v>
       </c>
@@ -9309,7 +9308,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>557</v>
       </c>
@@ -9332,7 +9331,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>119</v>
       </c>
@@ -9355,7 +9354,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>119</v>
       </c>
@@ -9378,7 +9377,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>12</v>
       </c>
@@ -9401,7 +9400,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>12</v>
       </c>
@@ -9424,7 +9423,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>516</v>
       </c>
@@ -9447,7 +9446,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>7</v>
       </c>
@@ -9470,7 +9469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>72</v>
       </c>
@@ -9493,7 +9492,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>554</v>
       </c>
@@ -9516,7 +9515,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>44</v>
       </c>
@@ -9539,7 +9538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>44</v>
       </c>
@@ -9562,7 +9561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>314</v>
       </c>
@@ -9585,7 +9584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>314</v>
       </c>
@@ -9608,7 +9607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>331</v>
       </c>
@@ -9631,7 +9630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>115</v>
       </c>
@@ -9639,7 +9638,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>117</v>
       </c>
@@ -9647,7 +9646,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>122</v>
       </c>
@@ -9655,7 +9654,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>126</v>
       </c>
@@ -9663,7 +9662,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>128</v>
       </c>
@@ -9671,7 +9670,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>130</v>
       </c>
@@ -9679,7 +9678,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>132</v>
       </c>
@@ -9687,7 +9686,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>134</v>
       </c>
@@ -9695,7 +9694,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>138</v>
       </c>
@@ -9703,7 +9702,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>140</v>
       </c>
@@ -9711,7 +9710,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>142</v>
       </c>
@@ -9719,7 +9718,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>144</v>
       </c>
@@ -9727,7 +9726,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>146</v>
       </c>
@@ -9735,7 +9734,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>148</v>
       </c>
@@ -9743,7 +9742,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>154</v>
       </c>
@@ -9751,7 +9750,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>158</v>
       </c>
@@ -9759,7 +9758,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>160</v>
       </c>
@@ -9767,7 +9766,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>162</v>
       </c>
@@ -9775,7 +9774,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>164</v>
       </c>
@@ -9783,7 +9782,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>166</v>
       </c>
@@ -9791,7 +9790,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>169</v>
       </c>
@@ -9799,7 +9798,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>171</v>
       </c>
@@ -9807,7 +9806,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>173</v>
       </c>
@@ -9815,7 +9814,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>175</v>
       </c>
@@ -9823,7 +9822,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>177</v>
       </c>
@@ -9831,7 +9830,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>179</v>
       </c>
@@ -9839,7 +9838,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>181</v>
       </c>
@@ -9847,7 +9846,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>183</v>
       </c>
@@ -9855,7 +9854,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>185</v>
       </c>
@@ -9863,7 +9862,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>187</v>
       </c>
@@ -9871,7 +9870,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>195</v>
       </c>
@@ -9879,7 +9878,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>197</v>
       </c>
@@ -9887,7 +9886,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>199</v>
       </c>
@@ -9895,7 +9894,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>201</v>
       </c>
@@ -9903,7 +9902,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>205</v>
       </c>
@@ -9911,7 +9910,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>207</v>
       </c>
@@ -9919,7 +9918,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>209</v>
       </c>
@@ -9927,7 +9926,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>211</v>
       </c>
@@ -9935,7 +9934,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>213</v>
       </c>
@@ -9943,7 +9942,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>215</v>
       </c>
@@ -9951,7 +9950,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>217</v>
       </c>
@@ -9959,7 +9958,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>219</v>
       </c>
@@ -9967,7 +9966,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>221</v>
       </c>
@@ -9975,7 +9974,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>223</v>
       </c>
@@ -9983,7 +9982,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>225</v>
       </c>
@@ -9991,7 +9990,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>227</v>
       </c>
@@ -9999,7 +9998,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>236</v>
       </c>
@@ -10007,7 +10006,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>238</v>
       </c>
@@ -10015,7 +10014,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>240</v>
       </c>
@@ -10023,7 +10022,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>242</v>
       </c>
@@ -10031,7 +10030,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>244</v>
       </c>
@@ -10039,7 +10038,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>246</v>
       </c>
@@ -10047,7 +10046,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>248</v>
       </c>
@@ -10055,7 +10054,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>250</v>
       </c>
@@ -10063,7 +10062,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>252</v>
       </c>
@@ -10071,7 +10070,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>254</v>
       </c>
@@ -10079,7 +10078,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>256</v>
       </c>
@@ -10087,7 +10086,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>258</v>
       </c>
@@ -10095,7 +10094,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>260</v>
       </c>
@@ -10103,7 +10102,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>262</v>
       </c>
@@ -10111,7 +10110,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>264</v>
       </c>
@@ -10119,7 +10118,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>266</v>
       </c>
@@ -10127,7 +10126,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>268</v>
       </c>
@@ -10135,7 +10134,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>270</v>
       </c>
@@ -10143,7 +10142,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>272</v>
       </c>
@@ -10151,7 +10150,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>274</v>
       </c>
@@ -10159,7 +10158,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>276</v>
       </c>
@@ -10167,7 +10166,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>278</v>
       </c>
@@ -10175,7 +10174,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>280</v>
       </c>
@@ -10183,7 +10182,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>282</v>
       </c>
@@ -10191,7 +10190,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>284</v>
       </c>
@@ -10199,7 +10198,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>289</v>
       </c>
@@ -10207,7 +10206,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>292</v>
       </c>
@@ -10215,7 +10214,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>296</v>
       </c>
@@ -10223,7 +10222,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>298</v>
       </c>
@@ -10231,7 +10230,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>300</v>
       </c>
@@ -10239,7 +10238,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>302</v>
       </c>
@@ -10247,7 +10246,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>304</v>
       </c>
@@ -10255,7 +10254,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>306</v>
       </c>
@@ -10263,7 +10262,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>308</v>
       </c>
@@ -10271,7 +10270,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>310</v>
       </c>
@@ -10279,7 +10278,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>312</v>
       </c>
@@ -10287,7 +10286,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>317</v>
       </c>
@@ -10295,7 +10294,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>323</v>
       </c>
@@ -10303,7 +10302,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>327</v>
       </c>
@@ -10311,7 +10310,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>329</v>
       </c>
@@ -10319,7 +10318,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>333</v>
       </c>
@@ -10327,7 +10326,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>335</v>
       </c>
@@ -10335,7 +10334,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>337</v>
       </c>
@@ -10343,7 +10342,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>346</v>
       </c>
@@ -10351,7 +10350,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>350</v>
       </c>
@@ -10359,7 +10358,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>352</v>
       </c>
@@ -10367,7 +10366,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>354</v>
       </c>
@@ -10375,7 +10374,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>356</v>
       </c>
@@ -10383,7 +10382,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>358</v>
       </c>
@@ -10391,7 +10390,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>360</v>
       </c>
@@ -10399,7 +10398,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>364</v>
       </c>
@@ -10407,7 +10406,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>366</v>
       </c>
@@ -10415,7 +10414,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>372</v>
       </c>
@@ -10423,7 +10422,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>374</v>
       </c>
@@ -10431,7 +10430,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>376</v>
       </c>
@@ -10439,7 +10438,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>378</v>
       </c>
@@ -10447,7 +10446,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>380</v>
       </c>
@@ -10455,7 +10454,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>382</v>
       </c>
@@ -10463,7 +10462,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>384</v>
       </c>
@@ -10471,7 +10470,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>386</v>
       </c>
@@ -10479,7 +10478,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>388</v>
       </c>
@@ -10487,7 +10486,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>390</v>
       </c>
@@ -10495,7 +10494,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>392</v>
       </c>
@@ -10503,7 +10502,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>394</v>
       </c>
@@ -10511,7 +10510,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>396</v>
       </c>
@@ -10519,7 +10518,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>398</v>
       </c>
@@ -10527,7 +10526,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>400</v>
       </c>
@@ -10535,7 +10534,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>402</v>
       </c>
@@ -10543,7 +10542,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>404</v>
       </c>
@@ -10551,7 +10550,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>406</v>
       </c>
@@ -10559,7 +10558,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>413</v>
       </c>
@@ -10567,7 +10566,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>415</v>
       </c>
@@ -10575,7 +10574,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>417</v>
       </c>
@@ -10583,7 +10582,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>419</v>
       </c>
@@ -10591,7 +10590,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>421</v>
       </c>
@@ -10599,7 +10598,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>423</v>
       </c>
@@ -10607,7 +10606,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>425</v>
       </c>
@@ -10615,7 +10614,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>427</v>
       </c>
@@ -10623,7 +10622,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>429</v>
       </c>
@@ -10631,7 +10630,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>431</v>
       </c>
@@ -10639,7 +10638,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>433</v>
       </c>
@@ -10647,7 +10646,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>441</v>
       </c>
@@ -10655,7 +10654,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>445</v>
       </c>
@@ -10663,7 +10662,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>449</v>
       </c>
@@ -10671,7 +10670,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>451</v>
       </c>
@@ -10679,7 +10678,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>458</v>
       </c>
@@ -10687,7 +10686,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>466</v>
       </c>
@@ -10695,7 +10694,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>468</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>470</v>
       </c>
@@ -10711,7 +10710,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>472</v>
       </c>
@@ -10719,7 +10718,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>474</v>
       </c>
@@ -10727,7 +10726,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>476</v>
       </c>
@@ -10735,7 +10734,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>480</v>
       </c>
@@ -10743,7 +10742,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>482</v>
       </c>
@@ -10751,7 +10750,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>484</v>
       </c>
@@ -10759,7 +10758,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>486</v>
       </c>
@@ -10767,7 +10766,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>488</v>
       </c>
@@ -10775,7 +10774,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>490</v>
       </c>
@@ -10783,7 +10782,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>492</v>
       </c>
@@ -10791,7 +10790,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>494</v>
       </c>
@@ -10799,7 +10798,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>496</v>
       </c>
@@ -10807,7 +10806,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>500</v>
       </c>
@@ -10815,7 +10814,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>502</v>
       </c>
@@ -10823,7 +10822,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>504</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>506</v>
       </c>
@@ -10839,7 +10838,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>508</v>
       </c>
@@ -10847,7 +10846,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>510</v>
       </c>
@@ -10855,7 +10854,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>512</v>
       </c>
@@ -10863,7 +10862,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>514</v>
       </c>
@@ -10871,7 +10870,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>520</v>
       </c>
@@ -10879,7 +10878,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>522</v>
       </c>
@@ -10887,7 +10886,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>524</v>
       </c>
@@ -10895,7 +10894,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>526</v>
       </c>
@@ -10903,7 +10902,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>528</v>
       </c>
@@ -10911,7 +10910,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>530</v>
       </c>
@@ -10919,7 +10918,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>532</v>
       </c>
@@ -10927,7 +10926,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>534</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>536</v>
       </c>
@@ -10943,7 +10942,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>538</v>
       </c>
@@ -10951,7 +10950,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>540</v>
       </c>
@@ -10959,7 +10958,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>542</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>544</v>
       </c>
@@ -10975,7 +10974,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>548</v>
       </c>
@@ -10983,7 +10982,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>559</v>
       </c>
@@ -10991,7 +10990,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>561</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>564</v>
       </c>
@@ -11007,7 +11006,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>566</v>
       </c>
@@ -11015,7 +11014,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>568</v>
       </c>
@@ -11023,7 +11022,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>570</v>
       </c>
@@ -11031,7 +11030,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>572</v>
       </c>
@@ -11039,7 +11038,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>574</v>
       </c>
@@ -11047,7 +11046,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>576</v>
       </c>
@@ -11055,7 +11054,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>578</v>
       </c>
@@ -11063,7 +11062,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>582</v>
       </c>
@@ -11071,7 +11070,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>584</v>
       </c>
@@ -11079,7 +11078,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>586</v>
       </c>
@@ -11087,7 +11086,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>588</v>
       </c>
@@ -11095,7 +11094,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>590</v>
       </c>
@@ -11103,7 +11102,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B504">
         <v>25</v>
       </c>
@@ -11111,7 +11110,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B505">
         <v>26</v>
       </c>
@@ -11119,7 +11118,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B506">
         <v>30</v>
       </c>
@@ -11127,7 +11126,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B507">
         <v>31</v>
       </c>
@@ -11135,7 +11134,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B508">
         <v>32</v>
       </c>
@@ -11143,7 +11142,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B509">
         <v>33</v>
       </c>
@@ -11151,7 +11150,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B510">
         <v>219</v>
       </c>
@@ -11159,7 +11158,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B511">
         <v>220</v>
       </c>
@@ -11167,7 +11166,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B512">
         <v>223</v>
       </c>
@@ -11175,7 +11174,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="513" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B513">
         <v>224</v>
       </c>
@@ -11183,7 +11182,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="514" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B514">
         <v>227</v>
       </c>
@@ -11191,7 +11190,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="515" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B515">
         <v>228</v>
       </c>
@@ -11199,7 +11198,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="516" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B516">
         <v>229</v>
       </c>
@@ -11207,7 +11206,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="517" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B517">
         <v>230</v>
       </c>
@@ -11215,7 +11214,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="518" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B518">
         <v>232</v>
       </c>
@@ -11223,7 +11222,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="519" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B519">
         <v>233</v>
       </c>
@@ -11231,7 +11230,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="520" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B520">
         <v>589</v>
       </c>
@@ -11239,7 +11238,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="521" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B521">
         <v>590</v>
       </c>
@@ -11247,7 +11246,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="522" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B522">
         <v>591</v>
       </c>
@@ -11255,7 +11254,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="523" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B523">
         <v>592</v>
       </c>
@@ -11263,7 +11262,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="524" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B524">
         <v>593</v>
       </c>
@@ -11271,7 +11270,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="525" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B525">
         <v>594</v>
       </c>
@@ -11279,7 +11278,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="526" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B526">
         <v>595</v>
       </c>
@@ -11287,7 +11286,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="527" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B527">
         <v>596</v>
       </c>
@@ -11295,7 +11294,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="528" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B528">
         <v>597</v>
       </c>
@@ -11303,7 +11302,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="529" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B529">
         <v>598</v>
       </c>
@@ -11311,7 +11310,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="530" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B530">
         <v>607</v>
       </c>
@@ -11319,7 +11318,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="531" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B531">
         <v>614</v>
       </c>
@@ -11327,7 +11326,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="532" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B532">
         <v>644</v>
       </c>
@@ -11335,7 +11334,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="533" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B533">
         <v>712</v>
       </c>
@@ -11343,7 +11342,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="534" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B534">
         <v>713</v>
       </c>
@@ -11351,7 +11350,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="535" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B535">
         <v>714</v>
       </c>
@@ -11359,7 +11358,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="536" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B536">
         <v>715</v>
       </c>
@@ -11367,7 +11366,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="537" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B537">
         <v>710</v>
       </c>
@@ -11375,7 +11374,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="538" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B538">
         <v>711</v>
       </c>
@@ -11383,7 +11382,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="539" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B539">
         <v>708</v>
       </c>
@@ -11391,7 +11390,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="540" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B540">
         <v>709</v>
       </c>
@@ -11399,7 +11398,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="541" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B541">
         <v>1034</v>
       </c>
@@ -11407,7 +11406,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="542" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B542">
         <v>1545</v>
       </c>
@@ -11415,7 +11414,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="543" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B543">
         <v>1546</v>
       </c>
@@ -11423,7 +11422,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="544" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B544">
         <v>655</v>
       </c>
@@ -11431,7 +11430,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B545">
         <v>657</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B546">
         <v>1672</v>
       </c>
@@ -11447,7 +11446,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B547">
         <v>900</v>
       </c>
@@ -11455,7 +11454,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B548">
         <v>901</v>
       </c>
@@ -11463,7 +11462,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B549">
         <v>902</v>
       </c>
@@ -11471,7 +11470,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B550">
         <v>903</v>
       </c>
@@ -11479,7 +11478,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B551">
         <v>1046</v>
       </c>
@@ -11487,7 +11486,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B552">
         <v>1870</v>
       </c>
@@ -11495,7 +11494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B553">
         <v>1884</v>
       </c>
@@ -11503,7 +11502,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B554">
         <v>1892</v>
       </c>
@@ -11511,7 +11510,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B555">
         <v>1893</v>
       </c>
@@ -11519,7 +11518,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B556">
         <v>1894</v>
       </c>
@@ -11527,7 +11526,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B557">
         <v>1895</v>
       </c>
@@ -11535,7 +11534,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B558">
         <v>1330</v>
       </c>
@@ -11543,7 +11542,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B559">
         <v>1166</v>
       </c>
@@ -11551,7 +11550,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B560">
         <v>1167</v>
       </c>
@@ -11559,7 +11558,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B561">
         <v>1168</v>
       </c>
@@ -11567,7 +11566,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B562">
         <v>381</v>
       </c>
@@ -11575,7 +11574,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B563">
         <v>705</v>
       </c>
@@ -11583,7 +11582,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B564">
         <v>706</v>
       </c>
@@ -11591,7 +11590,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B565">
         <v>707</v>
       </c>
@@ -11599,7 +11598,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B566">
         <v>1292</v>
       </c>
@@ -11607,7 +11606,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B567">
         <v>1293</v>
       </c>
@@ -11615,7 +11614,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B568">
         <v>1294</v>
       </c>
@@ -11623,7 +11622,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B569">
         <v>1296</v>
       </c>
@@ -11631,7 +11630,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B570">
         <v>1297</v>
       </c>
@@ -11639,7 +11638,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B571">
         <v>1298</v>
       </c>
@@ -11647,7 +11646,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B572">
         <v>1299</v>
       </c>
@@ -11655,7 +11654,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B573">
         <v>1300</v>
       </c>
@@ -11663,7 +11662,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B574">
         <v>1301</v>
       </c>
@@ -11671,7 +11670,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B575">
         <v>1303</v>
       </c>
@@ -11679,7 +11678,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B576">
         <v>1304</v>
       </c>
@@ -11687,7 +11686,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B577">
         <v>1305</v>
       </c>
@@ -11695,7 +11694,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B578">
         <v>1306</v>
       </c>
@@ -11703,7 +11702,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B579">
         <v>1307</v>
       </c>
@@ -11711,7 +11710,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B580">
         <v>1308</v>
       </c>
@@ -11719,7 +11718,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B581">
         <v>1318</v>
       </c>
@@ -11727,7 +11726,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B582">
         <v>1320</v>
       </c>
@@ -11735,7 +11734,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B583">
         <v>1321</v>
       </c>
@@ -11743,7 +11742,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B584">
         <v>1323</v>
       </c>
@@ -11751,7 +11750,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B585">
         <v>1324</v>
       </c>
@@ -11759,7 +11758,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B586">
         <v>1325</v>
       </c>
@@ -11767,7 +11766,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B587">
         <v>1326</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B588">
         <v>1327</v>
       </c>
@@ -11783,7 +11782,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B589">
         <v>1328</v>
       </c>
@@ -11791,7 +11790,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="590" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B590">
         <v>829</v>
       </c>
@@ -11799,7 +11798,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="591" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B591">
         <v>830</v>
       </c>
@@ -11807,7 +11806,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="592" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B592">
         <v>1505</v>
       </c>
@@ -11815,7 +11814,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="593" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B593">
         <v>696</v>
       </c>
@@ -11823,7 +11822,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="594" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B594">
         <v>697</v>
       </c>
@@ -11831,7 +11830,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="595" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B595">
         <v>700</v>
       </c>
@@ -11839,7 +11838,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="596" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B596">
         <v>701</v>
       </c>
@@ -11847,7 +11846,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="597" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B597">
         <v>702</v>
       </c>
@@ -11855,7 +11854,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="598" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B598">
         <v>703</v>
       </c>
@@ -11863,7 +11862,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="599" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B599">
         <v>704</v>
       </c>
@@ -11873,18 +11872,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G599" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="1122"/>
-        <filter val="1123"/>
-        <filter val="1124"/>
-        <filter val="1125"/>
-        <filter val="1126"/>
-        <filter val="1127"/>
-        <filter val="1128"/>
-        <filter val="1129"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A70:G300">
       <sortCondition ref="B1:B599"/>
     </sortState>
